--- a/lab_5/models/metrics/rf.xlsx
+++ b/lab_5/models/metrics/rf.xlsx
@@ -467,163 +467,163 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7178</v>
+        <v>0.7123</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7228</v>
+        <v>0.7266</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7285</v>
+        <v>0.7429</v>
       </c>
       <c r="D2" t="n">
-        <v>0.144</v>
+        <v>0.1426</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2404</v>
+        <v>0.2393</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1538</v>
+        <v>0.1527</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2311</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7002</v>
+        <v>0.7088</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6845</v>
+        <v>0.6862</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6667</v>
+        <v>0.6604</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1269</v>
+        <v>0.1306</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2132</v>
+        <v>0.2181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1235</v>
+        <v>0.1286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1892</v>
+        <v>0.1933</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7059</v>
+        <v>0.7098</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7094</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7133</v>
+        <v>0.6762</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1358</v>
+        <v>0.1322</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2281</v>
+        <v>0.2212</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1401</v>
+        <v>0.1328</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2147</v>
+        <v>0.2005</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7034</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6923</v>
+        <v>0.6996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.68</v>
+        <v>0.6952</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1299</v>
+        <v>0.1322</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2182</v>
+        <v>0.2222</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1291</v>
+        <v>0.1335</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1974</v>
+        <v>0.2047</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.7429</v>
+        <v>0.7104</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7052</v>
+        <v>0.7478</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6623</v>
+        <v>0.7905</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1466</v>
+        <v>0.1482</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2401</v>
+        <v>0.2496</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1553</v>
+        <v>0.1638</v>
       </c>
       <c r="G6" t="n">
-        <v>0.22</v>
+        <v>0.2532</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.714</v>
+        <v>0.7089</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7028</v>
+        <v>0.7109</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6901</v>
+        <v>0.713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1366</v>
+        <v>0.1372</v>
       </c>
       <c r="E7" t="n">
-        <v>0.228</v>
+        <v>0.2301</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1404</v>
+        <v>0.1423</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2105</v>
+        <v>0.2169</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0156</v>
+        <v>0.003</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0134</v>
+        <v>0.0229</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0262</v>
+        <v>0.0476</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0077</v>
+        <v>0.007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0111</v>
+        <v>0.0123</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0128</v>
+        <v>0.0136</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0152</v>
+        <v>0.0226</v>
       </c>
     </row>
   </sheetData>
